--- a/docs/paper/eric_lychee_paper_submission.xlsx
+++ b/docs/paper/eric_lychee_paper_submission.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rzhuang/Documents/VscodeProjects/lychee/docs/paper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DC5C2D-8BB5-1A41-88B6-F3ABC748CE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E04BF8F-D8A4-F84F-9642-410EE70C3992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2800" yWindow="820" windowWidth="33480" windowHeight="21680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1000" yWindow="660" windowWidth="33560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
   <si>
     <t>https://zenodo.org/records/22240717</t>
   </si>
@@ -151,9 +151,6 @@
     <t>2nd link to pay</t>
   </si>
   <si>
-    <t>https://idp-personal-authenticator.springernature.com/gateway?response_type=code&amp;redirect_uri=https%3A%2F%2Fidp.springernature.com%2Fauthed%2Fpersonal&amp;state=9e5e72fb-cbc1-4e5b-8b7a-fb754b3bee1f&amp;context_code=12870&amp;target_redirect_uri=https%3A%2F%2Fsubmission.springernature.com%2Fnew-submission%2F12870%2F3%3F_gl%3D1*1uwtuj6*_gcl_au*NzcwODAyMjU5LjE3ODg1NzI0MTA.*_ga*MTMwNzkxMzAyLjE3ODg1Njk0Mjc.*_ga_B3E4QL2TPR*czE3ODg1NzI0MTEkbzIkZzEkdDE3ODg1NzI0MjIkajQ5JGwwJGg3MTY3Nzk2NTQ.&amp;context_type=submission&amp;_gl=1*1uwtuj6*_gcl_au*NzcwODAyMjU5LjE3ODg1NzI0MTA.*_ga*MTMwNzkxMzAyLjE3ODg1Njk0Mjc.*_ga_B3E4QL2TPR*czE3ODg1NzI0MTEkbzIkZzEkdDE3ODg1NzI0MjIkajQ5JGwwJGg3MTY3Nzk2NTQ.</t>
-  </si>
-  <si>
     <t>PLOS ONE</t>
   </si>
   <si>
@@ -163,9 +160,6 @@
     <t>G3: Genes|Genomes|Genetics</t>
   </si>
   <si>
-    <t>https://oup2-ds.sams-sigma.com/?entityID=https%3A%2F%2Foup-sp.sams-sigma.com%2Fshibboleth&amp;return=https%3A%2F%2Foup-sp.sams-sigma.com%2FShibboleth.sso%2FLogin%3FSAMLDS%3D1%26target%3Dss%253Amem%253A18e9a470e4d6150b13cc7673dd2534f0a827ab3a88571544c4846a0444e8493c</t>
-  </si>
-  <si>
     <t>Has issue signed in</t>
   </si>
   <si>
@@ -185,12 +179,6 @@
   </si>
   <si>
     <t>BMC Genomics</t>
-  </si>
-  <si>
-    <t>https://orcid.org/oauth/authorize?client_id=APP-GBMYP31RJF9ISSZB&amp;response_type=code&amp;scope=%2Fread-limited&amp;redirect_uri=https:%2F%2Fidp-external-authenticator.springernature.com%2Forcid%2Fpost-auth&amp;state=10579e52-b130-4b55-aa2c-42fbbb374d8c</t>
-  </si>
-  <si>
-    <t>Log in with ORCID</t>
   </si>
   <si>
     <r>
@@ -213,17 +201,38 @@
     <t>orcid loging</t>
   </si>
   <si>
-    <t>unknown</t>
-  </si>
-  <si>
     <t>https://link.springer.com/journal/44372</t>
+  </si>
+  <si>
+    <t>Plant Environment Interactions</t>
+  </si>
+  <si>
+    <t>orcid login</t>
+  </si>
+  <si>
+    <t>https://onlinelibrary.wiley.com/journal/25756265</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>160 East 34th Street, New York, NY 10016</t>
+  </si>
+  <si>
+    <t>https://zenodo.org/records/22436625</t>
+  </si>
+  <si>
+    <t>v2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -287,6 +296,21 @@
       <color rgb="FF1155CC"/>
       <name val="Arial (Body)"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -305,10 +329,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -327,8 +352,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -545,22 +576,42 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="B2:B3"/>
+  <dimension ref="B1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E1" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E2" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="2" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="14" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B8" r:id="rId2" display="https://nyulangone.org/locations/perlmutter-cancer-center-34th-street" xr:uid="{A4F14556-9621-2948-968A-6B39BAA41A13}"/>
+    <hyperlink ref="E2" r:id="rId3" xr:uid="{3B285E5E-CAA4-D140-BB21-5103F9F2E95B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -571,13 +622,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W1000"/>
+  <dimension ref="A1:W1004"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.6640625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="41.33203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="44.33203125" style="11" customWidth="1"/>
     <col min="3" max="3" width="21.1640625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="11"/>
+    <col min="4" max="4" width="8.6640625" style="11" customWidth="1"/>
     <col min="5" max="5" width="7.83203125" style="11" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="11"/>
   </cols>
@@ -600,7 +651,7 @@
         <v>6</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -630,7 +681,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="E2" s="9">
         <v>2.8</v>
@@ -698,13 +749,13 @@
     </row>
     <row r="6" spans="1:23" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>60</v>
@@ -713,159 +764,182 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:23" ht="34" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1.9</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="5"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="8"/>
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="5"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="8"/>
+      <c r="E9" s="9"/>
+    </row>
+    <row r="10" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="5"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="8"/>
+      <c r="E10" s="9"/>
+    </row>
+    <row r="11" spans="1:23" ht="51" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B11" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E11" s="9">
         <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="356" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="9">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="51" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="9">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="170" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="9">
-        <v>2.4</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="9">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="51" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="9">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="51" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="9">
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="85" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+    <row r="17" spans="1:5" ht="85" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="E17" s="9">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="9">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="153" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="B18" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="9">
+      <c r="D18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="9">
         <v>3.9</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="8"/>
-    </row>
-    <row r="16" spans="1:23" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="8"/>
-    </row>
-    <row r="17" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="8"/>
-    </row>
-    <row r="18" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="8"/>
-    </row>
-    <row r="19" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
     </row>
-    <row r="20" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
     </row>
-    <row r="21" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
     </row>
-    <row r="22" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
     </row>
-    <row r="23" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
     </row>
-    <row r="24" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
     </row>
-    <row r="25" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
     </row>
-    <row r="26" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
     </row>
-    <row r="27" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
     </row>
-    <row r="28" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
     </row>
-    <row r="29" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
     </row>
-    <row r="30" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
     </row>
-    <row r="31" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
     </row>
-    <row r="32" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
     </row>
     <row r="33" spans="1:1" ht="16" x14ac:dyDescent="0.2">
@@ -3771,6 +3845,18 @@
     </row>
     <row r="1000" spans="1:1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1000" s="8"/>
+    </row>
+    <row r="1001" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1001" s="8"/>
+    </row>
+    <row r="1002" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1002" s="8"/>
+    </row>
+    <row r="1003" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1003" s="8"/>
+    </row>
+    <row r="1004" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1004" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3778,13 +3864,13 @@
     <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
     <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
     <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="B7" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="B8" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="B9" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="B10" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="B12" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="B13" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="B14" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="B11" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="B12" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="B13" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="B14" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="B16" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="B17" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="B18" r:id="rId11" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
